--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T12:54:49+00:00</t>
+    <t>2026-03-10T12:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T12:24:25+00:00</t>
+    <t>2026-03-11T12:27:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T12:27:06+00:00</t>
+    <t>2026-03-11T13:36:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T13:36:16+00:00</t>
+    <t>2026-03-11T13:36:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T13:36:49+00:00</t>
+    <t>2026-03-11T14:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:37+00:00</t>
+    <t>2026-03-11T14:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:51:01+00:00</t>
+    <t>2026-03-12T09:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:35:00+00:00</t>
+    <t>2026-03-12T09:36:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:36:07+00:00</t>
+    <t>2026-03-13T18:31:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T18:31:12+00:00</t>
+    <t>2026-03-13T19:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T19:05:40+00:00</t>
+    <t>2026-03-13T19:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T19:17:29+00:00</t>
+    <t>2026-03-13T19:33:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T19:33:48+00:00</t>
+    <t>2026-03-13T19:51:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T19:51:56+00:00</t>
+    <t>2026-03-13T19:52:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T15:02:13+00:00</t>
+    <t>2026-03-19T19:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T19:57:45+00:00</t>
+    <t>2026-03-19T19:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T19:58:27+00:00</t>
+    <t>2026-03-19T20:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:30:35+00:00</t>
+    <t>2026-03-20T06:49:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T06:49:44+00:00</t>
+    <t>2026-03-20T08:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:23:03+00:00</t>
+    <t>2026-03-20T09:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T09:00:21+00:00</t>
+    <t>2026-03-20T09:01:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T09:01:24+00:00</t>
+    <t>2026-03-27T10:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:52+00:00</t>
+    <t>2026-03-27T10:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:20:03+00:00</t>
+    <t>2026-03-27T10:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:28:06+00:00</t>
+    <t>2026-03-27T10:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:27:35+00:00</t>
+    <t>2026-04-07T13:07:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:07:42+00:00</t>
+    <t>2026-04-07T14:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:17:15+00:00</t>
+    <t>2026-04-07T14:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:19:36+00:00</t>
+    <t>2026-04-07T14:40:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:40:14+00:00</t>
+    <t>2026-04-07T14:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:41:24+00:00</t>
+    <t>2026-04-08T08:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:32:59+00:00</t>
+    <t>2026-04-08T08:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:34:49+00:00</t>
+    <t>2026-04-08T08:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:48:51+00:00</t>
+    <t>2026-04-08T08:50:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:50:28+00:00</t>
+    <t>2026-04-08T09:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:24:52+00:00</t>
+    <t>2026-04-08T09:39:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:39:30+00:00</t>
+    <t>2026-04-08T10:19:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T10:19:03+00:00</t>
+    <t>2026-04-08T10:26:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T10:26:49+00:00</t>
+    <t>2026-04-08T10:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T10:36:39+00:00</t>
+    <t>2026-04-08T19:23:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T19:23:52+00:00</t>
+    <t>2026-04-10T07:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T07:12:00+00:00</t>
+    <t>2026-04-10T07:44:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T07:44:22+00:00</t>
+    <t>2026-04-10T09:14:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T09:14:17+00:00</t>
+    <t>2026-04-10T09:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T09:31:22+00:00</t>
+    <t>2026-04-13T06:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T06:36:19+00:00</t>
+    <t>2026-04-13T06:42:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T06:42:00+00:00</t>
+    <t>2026-04-13T07:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T07:37:51+00:00</t>
+    <t>2026-04-16T09:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:46:31+00:00</t>
+    <t>2026-04-16T10:27:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:27:27+00:00</t>
+    <t>2026-04-16T10:30:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T19:26:05+00:00</t>
+    <t>2026-04-29T19:44:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T19:44:03+00:00</t>
+    <t>2026-04-29T20:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T20:17:30+00:00</t>
+    <t>2026-04-30T05:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T05:19:18+00:00</t>
+    <t>2026-04-30T05:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T05:43:24+00:00</t>
+    <t>2026-04-30T05:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T07:42:14+00:00</t>
+    <t>2026-05-11T08:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T08:23:33+00:00</t>
+    <t>2026-05-11T11:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:19:31+00:00</t>
+    <t>2026-05-11T11:43:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:43:47+00:00</t>
+    <t>2026-05-11T11:58:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:58:54+00:00</t>
+    <t>2026-05-11T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T12:29:55+00:00</t>
+    <t>2026-05-11T13:57:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T13:57:47+00:00</t>
+    <t>2026-05-12T07:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:05:21+00:00</t>
+    <t>2026-05-12T07:27:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:27:06+00:00</t>
+    <t>2026-05-12T08:37:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:37:01+00:00</t>
+    <t>2026-05-13T11:57:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T11:57:42+00:00</t>
+    <t>2026-05-18T09:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T09:58:38+00:00</t>
+    <t>2026-05-19T11:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:21:23+00:00</t>
+    <t>2026-05-27T10:50:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T10:50:22+00:00</t>
+    <t>2026-05-28T13:52:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T13:52:12+00:00</t>
+    <t>2026-05-31T18:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T10:54:08+00:00</t>
+    <t>2026-08-14T06:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T06:56:40+00:00</t>
+    <t>2026-08-19T13:18:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T13:18:51+00:00</t>
+    <t>2026-08-19T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T19:38:06+00:00</t>
+    <t>2026-08-20T07:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T07:53:34+00:00</t>
+    <t>2026-08-21T06:55:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-kommunenummer-alle.xlsx
+++ b/currentbuild/ValueSet-kommunenummer-alle.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.3</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T06:55:15+00:00</t>
+    <t>2026-08-24T07:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
